--- a/analysis_results/result_table.xlsx
+++ b/analysis_results/result_table.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/huanglinchun/Desktop/NTU/113_2/Operations Research/OR_final_project/analysis_results/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1954DBB7-5145-BD44-9FE0-2B1A845E689A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A995F155-2A57-F04C-92E9-9149C899EDEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -484,9 +484,6 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:N15"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14"/>
-  <cols>
-    <col min="14" max="14" width="10.59765625" bestFit="1" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1" spans="1:14">
       <c r="A1" s="1" t="s">
@@ -531,41 +528,41 @@
         <v>12</v>
       </c>
       <c r="B2">
-        <v>871.56600000000003</v>
+        <v>875.65599999999995</v>
       </c>
       <c r="C2">
-        <v>1370.5039999999999</v>
+        <v>1611.444</v>
       </c>
       <c r="D2">
-        <v>3540.0329999999999</v>
+        <v>3227.616</v>
       </c>
       <c r="E2">
-        <v>0.75379721036498804</v>
+        <v>0.72869882910482542</v>
       </c>
       <c r="F2">
-        <v>0.61285558637447735</v>
+        <v>0.50073242913655158</v>
       </c>
       <c r="G2">
-        <v>0.20499999999999999</v>
+        <v>0.67900000000000005</v>
       </c>
       <c r="H2">
-        <v>0.71699999999999997</v>
+        <v>4.8170000000000002</v>
       </c>
       <c r="I2">
-        <v>286.08999999999997</v>
+        <v>115.417</v>
       </c>
       <c r="J2">
-        <v>0.66500000000000004</v>
+        <v>0.67500000000000004</v>
       </c>
       <c r="K2">
-        <v>0.66300000000000003</v>
+        <v>0.64600000000000002</v>
       </c>
       <c r="L2">
-        <v>0.47899999999999998</v>
+        <v>0.45900000000000002</v>
       </c>
       <c r="N2" t="str">
-        <f>ROUND(A2, 2) &amp; " &amp; " &amp; ROUND(D2, 2) &amp; " &amp; " &amp; ROUND(B2, 2) &amp; " &amp; " &amp; ROUND(C2, 2) &amp; " &amp; " &amp; ROUND(E2, 2) &amp; " &amp; " &amp; ROUND(F2,2) &amp; " &amp; " &amp; ROUND(G2, 2) &amp; " &amp; " &amp; ROUND(H2, 2) &amp; " &amp; " &amp; ROUND(I2, 2) &amp; " &amp; " &amp; ROUND(J2,2) &amp; " &amp; " &amp; ROUND(K2, 2) &amp; " &amp; " &amp;ROUND(L2, 2) &amp; "\\"</f>
-        <v>1 &amp; 3540.03 &amp; 871.57 &amp; 1370.5 &amp; 0.75 &amp; 0.61 &amp; 0.21 &amp; 0.72 &amp; 286.09 &amp; 0.67 &amp; 0.66 &amp; 0.48\\</v>
+        <f>A2 &amp; " &amp; "&amp;ROUND(D2,2) &amp; " &amp; " &amp;ROUND(B2,2) &amp; " &amp; " &amp;ROUND(C2,2) &amp; " &amp; " &amp;ROUND(E2,2) &amp; " &amp; " &amp;ROUND(F2,2) &amp; " &amp; " &amp; ROUND(G2,2) &amp; " &amp; " &amp; ROUND(H2,2) &amp; " &amp; " &amp; ROUND(I2,2) &amp; " &amp; " &amp; ROUND(J2,3) &amp; " &amp; " &amp; ROUND(K2,3) &amp; " &amp; " &amp; ROUND(L2,3) &amp; "\\"</f>
+        <v>1 &amp; 3227.62 &amp; 875.66 &amp; 1611.44 &amp; 0.73 &amp; 0.5 &amp; 0.68 &amp; 4.82 &amp; 115.42 &amp; 0.675 &amp; 0.646 &amp; 0.459\\</v>
       </c>
     </row>
     <row r="3" spans="1:14">
@@ -573,41 +570,41 @@
         <v>13</v>
       </c>
       <c r="B3">
-        <v>2246.5039999999999</v>
+        <v>2156.3580000000002</v>
       </c>
       <c r="C3">
-        <v>2860.4140000000002</v>
+        <v>3163.3449999999998</v>
       </c>
       <c r="D3">
-        <v>6327.4660000000003</v>
+        <v>5582.36</v>
       </c>
       <c r="E3">
-        <v>0.64495992550572379</v>
+        <v>0.61371928718319846</v>
       </c>
       <c r="F3">
-        <v>0.54793688342221036</v>
+        <v>0.43333195995958701</v>
       </c>
       <c r="G3">
-        <v>0.84199999999999997</v>
+        <v>5.2910000000000004</v>
       </c>
       <c r="H3">
-        <v>2.95</v>
+        <v>18.748999999999999</v>
       </c>
       <c r="I3">
-        <v>214.30600000000001</v>
+        <v>227.43700000000001</v>
       </c>
       <c r="J3">
-        <v>0.59899999999999998</v>
+        <v>0.58899999999999997</v>
       </c>
       <c r="K3">
-        <v>0.626</v>
+        <v>0.60699999999999998</v>
       </c>
       <c r="L3">
-        <v>0.46800000000000003</v>
+        <v>0.47099999999999997</v>
       </c>
       <c r="N3" t="str">
-        <f t="shared" ref="N3:N15" si="0">ROUND(A3, 2) &amp; " &amp; " &amp; ROUND(D3, 2) &amp; " &amp; " &amp; ROUND(B3, 2) &amp; " &amp; " &amp; ROUND(C3, 2) &amp; " &amp; " &amp; ROUND(E3, 2) &amp; " &amp; " &amp; ROUND(F3,2) &amp; " &amp; " &amp; ROUND(G3, 2) &amp; " &amp; " &amp; ROUND(H3, 2) &amp; " &amp; " &amp; ROUND(I3, 2) &amp; " &amp; " &amp; ROUND(J3,2) &amp; " &amp; " &amp; ROUND(K3, 2) &amp; " &amp; " &amp;ROUND(L3, 2) &amp; "\\"</f>
-        <v>2 &amp; 6327.47 &amp; 2246.5 &amp; 2860.41 &amp; 0.64 &amp; 0.55 &amp; 0.84 &amp; 2.95 &amp; 214.31 &amp; 0.6 &amp; 0.63 &amp; 0.47\\</v>
+        <f t="shared" ref="N3:N15" si="0">A3 &amp; " &amp; "&amp;ROUND(D3,2) &amp; " &amp; " &amp;ROUND(B3,2) &amp; " &amp; " &amp;ROUND(C3,2) &amp; " &amp; " &amp;ROUND(E3,2) &amp; " &amp; " &amp;ROUND(F3,2) &amp; " &amp; " &amp; ROUND(G3,2) &amp; " &amp; " &amp; ROUND(H3,2) &amp; " &amp; " &amp; ROUND(I3,2) &amp; " &amp; " &amp; ROUND(J3,3) &amp; " &amp; " &amp; ROUND(K3,3) &amp; " &amp; " &amp; ROUND(L3,3) &amp; "\\"</f>
+        <v>2 &amp; 5582.36 &amp; 2156.36 &amp; 3163.35 &amp; 0.61 &amp; 0.43 &amp; 5.29 &amp; 18.75 &amp; 227.44 &amp; 0.589 &amp; 0.607 &amp; 0.471\\</v>
       </c>
     </row>
     <row r="4" spans="1:14">
@@ -615,41 +612,41 @@
         <v>14</v>
       </c>
       <c r="B4">
-        <v>4930.8220000000001</v>
+        <v>4352.9179999999997</v>
       </c>
       <c r="C4">
-        <v>5499.7169999999996</v>
+        <v>5563.4160000000002</v>
       </c>
       <c r="D4">
-        <v>10797.093000000001</v>
+        <v>9291.7189999999991</v>
       </c>
       <c r="E4">
-        <v>0.54331948423524745</v>
+        <v>0.53152715875286372</v>
       </c>
       <c r="F4">
-        <v>0.49062983897610218</v>
+        <v>0.4012500808515625</v>
       </c>
       <c r="G4">
-        <v>1.7090000000000001</v>
+        <v>27.760999999999999</v>
       </c>
       <c r="H4">
-        <v>5.4669999999999996</v>
+        <v>59.472000000000001</v>
       </c>
       <c r="I4">
-        <v>84.152000000000001</v>
+        <v>151.46</v>
       </c>
       <c r="J4">
-        <v>0.52800000000000002</v>
+        <v>0.53100000000000003</v>
       </c>
       <c r="K4">
-        <v>0.57499999999999996</v>
+        <v>0.48599999999999999</v>
       </c>
       <c r="L4">
-        <v>0.50700000000000001</v>
+        <v>0.49099999999999999</v>
       </c>
       <c r="N4" t="str">
         <f t="shared" si="0"/>
-        <v>3 &amp; 10797.09 &amp; 4930.82 &amp; 5499.72 &amp; 0.54 &amp; 0.49 &amp; 1.71 &amp; 5.47 &amp; 84.15 &amp; 0.53 &amp; 0.58 &amp; 0.51\\</v>
+        <v>3 &amp; 9291.72 &amp; 4352.92 &amp; 5563.42 &amp; 0.53 &amp; 0.4 &amp; 27.76 &amp; 59.47 &amp; 151.46 &amp; 0.531 &amp; 0.486 &amp; 0.491\\</v>
       </c>
     </row>
     <row r="5" spans="1:14">
@@ -657,41 +654,41 @@
         <v>15</v>
       </c>
       <c r="B5">
-        <v>2194.6990000000001</v>
+        <v>2133.6959999999999</v>
       </c>
       <c r="C5">
-        <v>2872.3249999999998</v>
+        <v>3070.1930000000002</v>
       </c>
       <c r="D5">
-        <v>5293.7309999999998</v>
+        <v>4883.1180000000004</v>
       </c>
       <c r="E5">
-        <v>0.58541546595397453</v>
+        <v>0.5630463978138559</v>
       </c>
       <c r="F5">
-        <v>0.45741009507283242</v>
+        <v>0.37126381135987302</v>
       </c>
       <c r="G5">
-        <v>0.66300000000000003</v>
+        <v>6.9939999999999998</v>
       </c>
       <c r="H5">
-        <v>2.0569999999999999</v>
+        <v>20.782</v>
       </c>
       <c r="I5">
-        <v>85.031999999999996</v>
+        <v>190.57900000000001</v>
       </c>
       <c r="J5">
-        <v>0.59899999999999998</v>
+        <v>0.58899999999999997</v>
       </c>
       <c r="K5">
-        <v>0.626</v>
+        <v>0.60699999999999998</v>
       </c>
       <c r="L5">
-        <v>0.47899999999999998</v>
+        <v>0.46300000000000002</v>
       </c>
       <c r="N5" t="str">
         <f t="shared" si="0"/>
-        <v>4 &amp; 5293.73 &amp; 2194.7 &amp; 2872.33 &amp; 0.59 &amp; 0.46 &amp; 0.66 &amp; 2.06 &amp; 85.03 &amp; 0.6 &amp; 0.63 &amp; 0.48\\</v>
+        <v>4 &amp; 4883.12 &amp; 2133.7 &amp; 3070.19 &amp; 0.56 &amp; 0.37 &amp; 6.99 &amp; 20.78 &amp; 190.58 &amp; 0.589 &amp; 0.607 &amp; 0.463\\</v>
       </c>
     </row>
     <row r="6" spans="1:14">
@@ -699,41 +696,41 @@
         <v>16</v>
       </c>
       <c r="B6">
-        <v>2142.8939999999998</v>
+        <v>2111.0329999999999</v>
       </c>
       <c r="C6">
-        <v>2884.2359999999999</v>
+        <v>2977.04</v>
       </c>
       <c r="D6">
-        <v>4742.5540000000001</v>
+        <v>4682.4080000000004</v>
       </c>
       <c r="E6">
-        <v>0.54815612009900161</v>
+        <v>0.54915654509389189</v>
       </c>
       <c r="F6">
-        <v>0.39183908079907998</v>
+        <v>0.36420747615329552</v>
       </c>
       <c r="G6">
-        <v>0.879</v>
+        <v>6.6269999999999998</v>
       </c>
       <c r="H6">
-        <v>1.6890000000000001</v>
+        <v>21.809000000000001</v>
       </c>
       <c r="I6">
-        <v>21.201000000000001</v>
+        <v>46.558999999999997</v>
       </c>
       <c r="J6">
-        <v>0.59899999999999998</v>
+        <v>0.58899999999999997</v>
       </c>
       <c r="K6">
-        <v>0.626</v>
+        <v>0.60699999999999998</v>
       </c>
       <c r="L6">
-        <v>0.46100000000000002</v>
+        <v>0.45500000000000002</v>
       </c>
       <c r="N6" t="str">
         <f t="shared" si="0"/>
-        <v>5 &amp; 4742.55 &amp; 2142.89 &amp; 2884.24 &amp; 0.55 &amp; 0.39 &amp; 0.88 &amp; 1.69 &amp; 21.2 &amp; 0.6 &amp; 0.63 &amp; 0.46\\</v>
+        <v>5 &amp; 4682.41 &amp; 2111.03 &amp; 2977.04 &amp; 0.55 &amp; 0.36 &amp; 6.63 &amp; 21.81 &amp; 46.56 &amp; 0.589 &amp; 0.607 &amp; 0.455\\</v>
       </c>
     </row>
     <row r="7" spans="1:14">
@@ -741,41 +738,41 @@
         <v>17</v>
       </c>
       <c r="B7">
-        <v>2248.1550000000002</v>
+        <v>1413.088</v>
       </c>
       <c r="C7">
-        <v>2877.0970000000002</v>
+        <v>1954.5719999999999</v>
       </c>
       <c r="D7">
-        <v>6327.5649999999996</v>
+        <v>4134.308</v>
       </c>
       <c r="E7">
-        <v>0.64470455854661302</v>
+        <v>0.65820446855918824</v>
       </c>
       <c r="F7">
-        <v>0.5453073970792871</v>
+        <v>0.52723115936209874</v>
       </c>
       <c r="G7">
-        <v>0.75900000000000001</v>
+        <v>8.1120000000000001</v>
       </c>
       <c r="H7">
-        <v>2.1469999999999998</v>
+        <v>21.306999999999999</v>
       </c>
       <c r="I7">
-        <v>168.923</v>
+        <v>298.67899999999997</v>
       </c>
       <c r="J7">
-        <v>0.60399999999999998</v>
+        <v>0.56200000000000006</v>
       </c>
       <c r="K7">
-        <v>0.63</v>
+        <v>0.501</v>
       </c>
       <c r="L7">
-        <v>0.47</v>
+        <v>0.46400000000000002</v>
       </c>
       <c r="N7" t="str">
         <f t="shared" si="0"/>
-        <v>6 &amp; 6327.57 &amp; 2248.16 &amp; 2877.1 &amp; 0.64 &amp; 0.55 &amp; 0.76 &amp; 2.15 &amp; 168.92 &amp; 0.6 &amp; 0.63 &amp; 0.47\\</v>
+        <v>6 &amp; 4134.31 &amp; 1413.09 &amp; 1954.57 &amp; 0.66 &amp; 0.53 &amp; 8.11 &amp; 21.31 &amp; 298.68 &amp; 0.562 &amp; 0.501 &amp; 0.464\\</v>
       </c>
     </row>
     <row r="8" spans="1:14">
@@ -783,41 +780,41 @@
         <v>18</v>
       </c>
       <c r="B8">
-        <v>2280.4499999999998</v>
+        <v>2687.5030000000002</v>
       </c>
       <c r="C8">
-        <v>2862.4650000000001</v>
+        <v>3909.5790000000002</v>
       </c>
       <c r="D8">
-        <v>6327.6549999999997</v>
+        <v>6850.2169999999996</v>
       </c>
       <c r="E8">
-        <v>0.63960582553884493</v>
+        <v>0.60767622397947396</v>
       </c>
       <c r="F8">
-        <v>0.54762625332765447</v>
+        <v>0.4292766199961256</v>
       </c>
       <c r="G8">
-        <v>0.64100000000000001</v>
+        <v>3.5659999999999998</v>
       </c>
       <c r="H8">
-        <v>2.2200000000000002</v>
+        <v>14.837</v>
       </c>
       <c r="I8">
-        <v>178.26599999999999</v>
+        <v>480.52499999999998</v>
       </c>
       <c r="J8">
-        <v>0.59399999999999997</v>
+        <v>0.625</v>
       </c>
       <c r="K8">
-        <v>0.624</v>
+        <v>0.63800000000000001</v>
       </c>
       <c r="L8">
         <v>0.47099999999999997</v>
       </c>
       <c r="N8" t="str">
         <f t="shared" si="0"/>
-        <v>7 &amp; 6327.66 &amp; 2280.45 &amp; 2862.47 &amp; 0.64 &amp; 0.55 &amp; 0.64 &amp; 2.22 &amp; 178.27 &amp; 0.59 &amp; 0.62 &amp; 0.47\\</v>
+        <v>7 &amp; 6850.22 &amp; 2687.5 &amp; 3909.58 &amp; 0.61 &amp; 0.43 &amp; 3.57 &amp; 14.84 &amp; 480.53 &amp; 0.625 &amp; 0.638 &amp; 0.471\\</v>
       </c>
     </row>
     <row r="9" spans="1:14">
@@ -828,29 +825,29 @@
         <v>72.849000000000004</v>
       </c>
       <c r="C9">
-        <v>212.33799999999999</v>
+        <v>65.963999999999999</v>
       </c>
       <c r="D9">
-        <v>735.83699999999999</v>
+        <v>723.54899999999998</v>
       </c>
       <c r="E9">
-        <v>0.90099845482083663</v>
+        <v>0.89931711604880937</v>
       </c>
       <c r="F9">
-        <v>0.71143337451093114</v>
+        <v>0.90883271208998984</v>
       </c>
       <c r="G9">
-        <v>2.8000000000000001E-2</v>
+        <v>4.5999999999999999E-2</v>
       </c>
       <c r="H9">
-        <v>7.8E-2</v>
+        <v>5.6000000000000001E-2</v>
       </c>
       <c r="I9">
-        <v>20.027999999999999</v>
+        <v>13.891</v>
       </c>
       <c r="N9" t="str">
-        <f>A9 &amp; " &amp; " &amp; ROUND(D9, 2) &amp; " &amp; " &amp; ROUND(B9, 2) &amp; " &amp; " &amp; ROUND(C9, 2) &amp; " &amp; " &amp; ROUND(E9, 2) &amp; " &amp; " &amp; ROUND(F9,2) &amp; " &amp; " &amp; ROUND(G9, 2) &amp; " &amp; " &amp; ROUND(H9, 2) &amp; " &amp; " &amp; ROUND(I9, 2) &amp; " &amp; " &amp; " &amp; " &amp; " &amp; "&amp; "\\"</f>
-        <v>1_np &amp; 735.84 &amp; 72.85 &amp; 212.34 &amp; 0.9 &amp; 0.71 &amp; 0.03 &amp; 0.08 &amp; 20.03 &amp;  &amp;  &amp; \\</v>
+        <f t="shared" si="0"/>
+        <v>1_np &amp; 723.55 &amp; 72.85 &amp; 65.96 &amp; 0.9 &amp; 0.91 &amp; 0.05 &amp; 0.06 &amp; 13.89 &amp; 0 &amp; 0 &amp; 0\\</v>
       </c>
     </row>
     <row r="10" spans="1:14">
@@ -861,29 +858,29 @@
         <v>287.00099999999998</v>
       </c>
       <c r="C10">
-        <v>521.65599999999995</v>
+        <v>205.19499999999999</v>
       </c>
       <c r="D10">
-        <v>1360.6479999999999</v>
+        <v>1314.097</v>
       </c>
       <c r="E10">
-        <v>0.78907035471334241</v>
+        <v>0.78159831427969173</v>
       </c>
       <c r="F10">
-        <v>0.61661208483016916</v>
+        <v>0.8438509485981629</v>
       </c>
       <c r="G10">
-        <v>6.7000000000000004E-2</v>
+        <v>0.12</v>
       </c>
       <c r="H10">
-        <v>0.20200000000000001</v>
+        <v>0.217</v>
       </c>
       <c r="I10">
-        <v>22.466999999999999</v>
+        <v>12.771000000000001</v>
       </c>
       <c r="N10" t="str">
-        <f t="shared" ref="N10:N15" si="1">A10 &amp; " &amp; " &amp; ROUND(D10, 2) &amp; " &amp; " &amp; ROUND(B10, 2) &amp; " &amp; " &amp; ROUND(C10, 2) &amp; " &amp; " &amp; ROUND(E10, 2) &amp; " &amp; " &amp; ROUND(F10,2) &amp; " &amp; " &amp; ROUND(G10, 2) &amp; " &amp; " &amp; ROUND(H10, 2) &amp; " &amp; " &amp; ROUND(I10, 2) &amp; " &amp; " &amp; " &amp; " &amp; " &amp; "&amp; "\\"</f>
-        <v>2_np &amp; 1360.65 &amp; 287 &amp; 521.66 &amp; 0.79 &amp; 0.62 &amp; 0.07 &amp; 0.2 &amp; 22.47 &amp;  &amp;  &amp; \\</v>
+        <f t="shared" si="0"/>
+        <v>2_np &amp; 1314.1 &amp; 287 &amp; 205.2 &amp; 0.78 &amp; 0.84 &amp; 0.12 &amp; 0.22 &amp; 12.77 &amp; 0 &amp; 0 &amp; 0\\</v>
       </c>
     </row>
     <row r="11" spans="1:14">
@@ -891,32 +888,32 @@
         <v>21</v>
       </c>
       <c r="B11">
-        <v>487.46100000000001</v>
+        <v>486.983</v>
       </c>
       <c r="C11">
-        <v>734.94200000000001</v>
+        <v>528.06100000000004</v>
       </c>
       <c r="D11">
-        <v>1899.644</v>
+        <v>1815.27</v>
       </c>
       <c r="E11">
-        <v>0.74339349899244278</v>
+        <v>0.73172971513879481</v>
       </c>
       <c r="F11">
-        <v>0.61311593119552932</v>
+        <v>0.70910057457017406</v>
       </c>
       <c r="G11">
-        <v>0.14099999999999999</v>
+        <v>0.28699999999999998</v>
       </c>
       <c r="H11">
-        <v>0.40100000000000002</v>
+        <v>0.72499999999999998</v>
       </c>
       <c r="I11">
-        <v>19.161000000000001</v>
+        <v>22.082999999999998</v>
       </c>
       <c r="N11" t="str">
-        <f t="shared" si="1"/>
-        <v>3_np &amp; 1899.64 &amp; 487.46 &amp; 734.94 &amp; 0.74 &amp; 0.61 &amp; 0.14 &amp; 0.4 &amp; 19.16 &amp;  &amp;  &amp; \\</v>
+        <f t="shared" si="0"/>
+        <v>3_np &amp; 1815.27 &amp; 486.98 &amp; 528.06 &amp; 0.73 &amp; 0.71 &amp; 0.29 &amp; 0.73 &amp; 22.08 &amp; 0 &amp; 0 &amp; 0\\</v>
       </c>
     </row>
     <row r="12" spans="1:14">
@@ -927,29 +924,29 @@
         <v>318.50700000000001</v>
       </c>
       <c r="C12">
-        <v>546.00400000000002</v>
+        <v>206.99</v>
       </c>
       <c r="D12">
-        <v>1172.3879999999999</v>
+        <v>1150.172</v>
       </c>
       <c r="E12">
-        <v>0.72832628788421572</v>
+        <v>0.72307880908246758</v>
       </c>
       <c r="F12">
-        <v>0.53428046005247409</v>
+        <v>0.8200356120649781</v>
       </c>
       <c r="G12">
-        <v>7.2999999999999995E-2</v>
+        <v>0.12</v>
       </c>
       <c r="H12">
-        <v>0.192</v>
+        <v>0.20499999999999999</v>
       </c>
       <c r="I12">
-        <v>12.305</v>
+        <v>9.6340000000000003</v>
       </c>
       <c r="N12" t="str">
-        <f t="shared" si="1"/>
-        <v>4_np &amp; 1172.39 &amp; 318.51 &amp; 546 &amp; 0.73 &amp; 0.53 &amp; 0.07 &amp; 0.19 &amp; 12.31 &amp;  &amp;  &amp; \\</v>
+        <f t="shared" si="0"/>
+        <v>4_np &amp; 1150.17 &amp; 318.51 &amp; 206.99 &amp; 0.72 &amp; 0.82 &amp; 0.12 &amp; 0.21 &amp; 9.63 &amp; 0 &amp; 0 &amp; 0\\</v>
       </c>
     </row>
     <row r="13" spans="1:14">
@@ -960,29 +957,29 @@
         <v>350.01400000000001</v>
       </c>
       <c r="C13">
-        <v>570.35199999999998</v>
+        <v>208.786</v>
       </c>
       <c r="D13">
-        <v>1110.9780000000001</v>
+        <v>1109.711</v>
       </c>
       <c r="E13">
-        <v>0.68494965696890486</v>
+        <v>0.68458995179826099</v>
       </c>
       <c r="F13">
-        <v>0.48662169727933408</v>
+        <v>0.8118555191396678</v>
       </c>
       <c r="G13">
-        <v>6.2E-2</v>
+        <v>0.16700000000000001</v>
       </c>
       <c r="H13">
-        <v>0.23</v>
+        <v>0.20200000000000001</v>
       </c>
       <c r="I13">
-        <v>2.8450000000000002</v>
+        <v>3.423</v>
       </c>
       <c r="N13" t="str">
-        <f t="shared" si="1"/>
-        <v>5_np &amp; 1110.98 &amp; 350.01 &amp; 570.35 &amp; 0.68 &amp; 0.49 &amp; 0.06 &amp; 0.23 &amp; 2.85 &amp;  &amp;  &amp; \\</v>
+        <f t="shared" si="0"/>
+        <v>5_np &amp; 1109.71 &amp; 350.01 &amp; 208.79 &amp; 0.68 &amp; 0.81 &amp; 0.17 &amp; 0.2 &amp; 3.42 &amp; 0 &amp; 0 &amp; 0\\</v>
       </c>
     </row>
     <row r="14" spans="1:14">
@@ -990,32 +987,32 @@
         <v>24</v>
       </c>
       <c r="B14">
-        <v>276.68299999999999</v>
+        <v>195.63200000000001</v>
       </c>
       <c r="C14">
-        <v>532.68600000000004</v>
+        <v>254.54300000000001</v>
       </c>
       <c r="D14">
-        <v>1360.6479999999999</v>
+        <v>1026.5840000000001</v>
       </c>
       <c r="E14">
-        <v>0.79665350627054166</v>
+        <v>0.80943400637453922</v>
       </c>
       <c r="F14">
-        <v>0.6085056531887747</v>
+        <v>0.75204854157087975</v>
       </c>
       <c r="G14">
-        <v>6.8000000000000005E-2</v>
+        <v>0.14799999999999999</v>
       </c>
       <c r="H14">
-        <v>0.318</v>
+        <v>0.45700000000000002</v>
       </c>
       <c r="I14">
-        <v>22.888000000000002</v>
+        <v>16.588000000000001</v>
       </c>
       <c r="N14" t="str">
-        <f t="shared" si="1"/>
-        <v>6_np &amp; 1360.65 &amp; 276.68 &amp; 532.69 &amp; 0.8 &amp; 0.61 &amp; 0.07 &amp; 0.32 &amp; 22.89 &amp;  &amp;  &amp; \\</v>
+        <f t="shared" si="0"/>
+        <v>6_np &amp; 1026.58 &amp; 195.63 &amp; 254.54 &amp; 0.81 &amp; 0.75 &amp; 0.15 &amp; 0.46 &amp; 16.59 &amp; 0 &amp; 0 &amp; 0\\</v>
       </c>
     </row>
     <row r="15" spans="1:14">
@@ -1023,32 +1020,32 @@
         <v>25</v>
       </c>
       <c r="B15">
-        <v>287.00099999999998</v>
+        <v>313.01900000000001</v>
       </c>
       <c r="C15">
-        <v>529.07100000000003</v>
+        <v>635.505</v>
       </c>
       <c r="D15">
-        <v>1360.6479999999999</v>
+        <v>1542.348</v>
       </c>
       <c r="E15">
-        <v>0.78907035471334241</v>
+        <v>0.79705034142748588</v>
       </c>
       <c r="F15">
-        <v>0.61116247552636682</v>
+        <v>0.58796263878190913</v>
       </c>
       <c r="G15">
-        <v>6.9000000000000006E-2</v>
+        <v>0.113</v>
       </c>
       <c r="H15">
-        <v>0.20300000000000001</v>
+        <v>0.48899999999999999</v>
       </c>
       <c r="I15">
-        <v>24.047000000000001</v>
+        <v>24.366</v>
       </c>
       <c r="N15" t="str">
-        <f t="shared" si="1"/>
-        <v>7_np &amp; 1360.65 &amp; 287 &amp; 529.07 &amp; 0.79 &amp; 0.61 &amp; 0.07 &amp; 0.2 &amp; 24.05 &amp;  &amp;  &amp; \\</v>
+        <f t="shared" si="0"/>
+        <v>7_np &amp; 1542.35 &amp; 313.02 &amp; 635.51 &amp; 0.8 &amp; 0.59 &amp; 0.11 &amp; 0.49 &amp; 24.37 &amp; 0 &amp; 0 &amp; 0\\</v>
       </c>
     </row>
   </sheetData>
